--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="515">
   <si>
     <t>Filename</t>
   </si>
@@ -811,751 +811,754 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9334,0.0103,0.0156,0.0034</t>
-  </si>
-  <si>
-    <t>0.0162,0.0048,0.0001,0.9918</t>
-  </si>
-  <si>
-    <t>0.9983,0.0006,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.3681,0.0011,0.0001,0.7957</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9807,0.0150,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9916,0.0102,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9609,0.0444,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9601,0.0558,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9951,0.0035,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0370,0.9129,0.0312,0.0008</t>
-  </si>
-  <si>
-    <t>0.0691,0.1518,0.5390,0.0009</t>
-  </si>
-  <si>
-    <t>0.0112,0.0424,0.9541,0.0002</t>
-  </si>
-  <si>
-    <t>0.0078,0.0107,0.9805,0.0007</t>
-  </si>
-  <si>
-    <t>0.9805,0.0017,0.0040,0.0001</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.9839,0.0036,0.0022,0.0006</t>
+  </si>
+  <si>
+    <t>0.0201,0.0013,0.0000,0.9901</t>
+  </si>
+  <si>
+    <t>0.9975,0.0006,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.2171,0.0017,0.0000,0.8737</t>
+  </si>
+  <si>
+    <t>0.9975,0.0015,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9629,0.0303,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9855,0.0161,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9932,0.0048,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9569,0.0533,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9971,0.0021,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.7006,0.2260,0.0093,0.0008</t>
+  </si>
+  <si>
+    <t>0.0044,0.0118,0.9881,0.0001</t>
+  </si>
+  <si>
+    <t>0.1149,0.0413,0.7520,0.0002</t>
+  </si>
+  <si>
+    <t>0.0541,0.0071,0.9177,0.0008</t>
+  </si>
+  <si>
+    <t>0.9763,0.0023,0.0056,0.0001</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0011,0.9976,0.0003,0.0000</t>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.9958,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9562,0.0010,0.0368,0.0003</t>
+  </si>
+  <si>
+    <t>0.6521,0.0034,0.3528,0.0014</t>
+  </si>
+  <si>
+    <t>0.0014,0.0011,0.9971,0.0001</t>
+  </si>
+  <si>
+    <t>0.0057,0.0070,0.9840,0.0006</t>
+  </si>
+  <si>
+    <t>0.0014,0.0005,0.9977,0.0001</t>
+  </si>
+  <si>
+    <t>0.0093,0.0005,0.9895,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.9971,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.2496,0.7790,0.0036,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9998,0.0013</t>
+  </si>
+  <si>
+    <t>0.0009,0.9974,0.0027,0.0000</t>
+  </si>
+  <si>
+    <t>0.8590,0.1618,0.0025,0.0005</t>
+  </si>
+  <si>
+    <t>0.5938,0.2615,0.0634,0.0019</t>
+  </si>
+  <si>
+    <t>0.0073,0.9910,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9983,0.0320,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.9947,0.0040,0.0002</t>
+  </si>
+  <si>
+    <t>0.0095,0.0019,0.9750,0.0034</t>
+  </si>
+  <si>
+    <t>0.0027,0.9237,0.3227,0.0006</t>
+  </si>
+  <si>
+    <t>0.3326,0.0008,0.7010,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.1903,0.9915,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0030,0.9985,0.0002</t>
+  </si>
+  <si>
+    <t>0.0030,0.8455,0.0036,0.9358</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0043,0.0089,0.9859,0.0024</t>
+  </si>
+  <si>
+    <t>0.0025,0.2706,0.9626,0.0001</t>
+  </si>
+  <si>
+    <t>0.0354,0.0182,0.9220,0.0073</t>
+  </si>
+  <si>
+    <t>0.0006,0.0008,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.0083,0.9936,0.0001</t>
+  </si>
+  <si>
+    <t>0.1150,0.0730,0.6101,0.0035</t>
+  </si>
+  <si>
+    <t>0.9948,0.0063,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9906,0.0057,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.9900,0.0118,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0123,0.9989,0.0007</t>
+  </si>
+  <si>
+    <t>0.9972,0.0014,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9923,0.0066,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9865,0.0161,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.3863,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0472,0.9934,0.0002</t>
+  </si>
+  <si>
+    <t>0.0213,0.2004,0.6485,0.0039</t>
+  </si>
+  <si>
+    <t>0.0000,0.9961,0.9794,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0050,0.9984,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.9993,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0828,0.0093,0.9077,0.0003</t>
+  </si>
+  <si>
+    <t>0.8475,0.1348,0.0032,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0011,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9986,0.0992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9885,0.0868,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.0934,0.0000</t>
+  </si>
+  <si>
+    <t>0.0133,0.0003,0.0148,0.9921</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0146,0.9994</t>
+  </si>
+  <si>
+    <t>0.0025,0.0002,0.0003,0.9986</t>
+  </si>
+  <si>
+    <t>0.0012,0.0002,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.0002,0.9990,0.0080,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9955,0.1965,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9927,0.1516,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9891,0.3260,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.0618,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.0680,0.0000</t>
+  </si>
+  <si>
+    <t>0.9882,0.0192,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9642,0.0569,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9235,0.1393,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0009,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9935,0.0071,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9771,0.0287,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9895,0.0083,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9647,0.0543,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9894,0.0128,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0012,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9959,0.0033,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.1331,0.1109,0.6237,0.0009</t>
+  </si>
+  <si>
+    <t>0.9745,0.0005,0.0187,0.0001</t>
+  </si>
+  <si>
+    <t>0.0152,0.0009,0.9853,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.7798,0.0120,0.1548,0.0010</t>
-  </si>
-  <si>
-    <t>0.3069,0.0096,0.6659,0.0007</t>
-  </si>
-  <si>
-    <t>0.0009,0.0004,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0478,0.0224,0.8889,0.0011</t>
-  </si>
-  <si>
-    <t>0.0019,0.0006,0.9971,0.0001</t>
-  </si>
-  <si>
-    <t>0.0132,0.0005,0.9846,0.0006</t>
-  </si>
-  <si>
-    <t>0.0007,0.0002,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.9988,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.2906,0.6350,0.0296,0.0011</t>
-  </si>
-  <si>
-    <t>0.0006,0.0046,0.9987,0.0076</t>
-  </si>
-  <si>
-    <t>0.0018,0.9972,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.8108,0.2010,0.0050,0.0010</t>
-  </si>
-  <si>
-    <t>0.7031,0.1065,0.0931,0.0011</t>
-  </si>
-  <si>
-    <t>0.0237,0.9783,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9984,0.0745,0.0000</t>
-  </si>
-  <si>
-    <t>0.0048,0.9782,0.0144,0.0020</t>
-  </si>
-  <si>
-    <t>0.0036,0.0036,0.9920,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.3656,0.9751,0.0001</t>
-  </si>
-  <si>
-    <t>0.0892,0.0002,0.9220,0.0002</t>
-  </si>
-  <si>
-    <t>0.0013,0.4168,0.9486,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.0055,0.9933,0.0003</t>
-  </si>
-  <si>
-    <t>0.0025,0.8844,0.0010,0.8402</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9992,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0128,0.0123,0.9683,0.0005</t>
-  </si>
-  <si>
-    <t>0.0114,0.0528,0.9625,0.0003</t>
-  </si>
-  <si>
-    <t>0.4009,0.0014,0.6422,0.0009</t>
-  </si>
-  <si>
-    <t>0.0004,0.0019,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0221,0.0083,0.9646,0.0009</t>
-  </si>
-  <si>
-    <t>0.0012,0.0341,0.9934,0.0002</t>
-  </si>
-  <si>
-    <t>0.9351,0.1014,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0019,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9891,0.0122,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0230,0.9985,0.0004</t>
-  </si>
-  <si>
-    <t>0.9978,0.0014,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9895,0.0106,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9804,0.0239,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.4404,0.0000</t>
-  </si>
-  <si>
-    <t>0.0114,0.1198,0.9091,0.0009</t>
-  </si>
-  <si>
-    <t>0.0551,0.1326,0.5898,0.0076</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.8764,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.9950,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.6584,0.0062,0.3135,0.0005</t>
-  </si>
-  <si>
-    <t>0.2683,0.4166,0.0892,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.0011,0.9997,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.1010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9946,0.0187,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9988,0.0065,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.0001,0.1279,0.9875</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0159,0.0000,0.0000,0.9977</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0008,0.9999</t>
-  </si>
-  <si>
-    <t>0.0017,0.0001,0.0003,0.9990</t>
-  </si>
-  <si>
-    <t>0.0013,0.0007,0.0000,0.9995</t>
-  </si>
-  <si>
-    <t>0.0002,0.9991,0.0026,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9870,0.3091,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9951,0.0241,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9963,0.1897,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.1023,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9991,0.0899,0.0000</t>
-  </si>
-  <si>
-    <t>0.9199,0.1215,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.8972,0.1589,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9216,0.1211,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0021,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9860,0.0166,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9887,0.0104,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9349,0.0991,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9915,0.0102,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9893,0.0127,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0032,0.0096,0.9907,0.0001</t>
-  </si>
-  <si>
-    <t>0.9879,0.0003,0.0051,0.0001</t>
-  </si>
-  <si>
-    <t>0.0469,0.0021,0.9569,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9990,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0327,0.9749,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.1249,0.0185,0.7709,0.0019</t>
-  </si>
-  <si>
-    <t>0.6632,0.0110,0.2451,0.0014</t>
-  </si>
-  <si>
-    <t>0.7077,0.1967,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.5359,0.1033,0.1753,0.0023</t>
-  </si>
-  <si>
-    <t>0.0005,0.5500,0.0011,0.9526</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9972,0.2562,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9995,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0086,0.9901,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0549,0.9505,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.9899,0.0079,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9925,0.0016,0.0032,0.0004</t>
-  </si>
-  <si>
-    <t>0.9967,0.0015,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9564,0.0409,0.0042,0.0002</t>
-  </si>
-  <si>
-    <t>0.9974,0.0014,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9974,0.0010,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9850,0.7481,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9904,0.1918,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9806,0.4365,0.0001</t>
-  </si>
-  <si>
-    <t>0.4652,0.0104,0.4575,0.0008</t>
-  </si>
-  <si>
-    <t>0.9810,0.0005,0.0102,0.0002</t>
-  </si>
-  <si>
-    <t>0.8576,0.0399,0.0285,0.0015</t>
-  </si>
-  <si>
-    <t>0.3580,0.0010,0.7484,0.0002</t>
-  </si>
-  <si>
-    <t>0.9273,0.0168,0.0118,0.0006</t>
-  </si>
-  <si>
-    <t>0.5510,0.0003,0.0003,0.6681</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0010,0.0012,0.9990</t>
-  </si>
-  <si>
-    <t>0.0028,0.0000,0.0003,0.9990</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0124,0.0000</t>
-  </si>
-  <si>
-    <t>0.9808,0.0164,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9980,0.0003,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.0026,0.9957,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.7525,0.0007,0.0209,0.1085</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0058,0.9968,0.0068</t>
-  </si>
-  <si>
-    <t>0.9577,0.0003,0.0162,0.0049</t>
-  </si>
-  <si>
-    <t>0.9979,0.0004,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.0057,0.9947,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9854,0.0065,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.9789,0.0094,0.0031,0.0003</t>
-  </si>
-  <si>
-    <t>0.0029,0.9958,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.5122,0.4037,0.0224,0.0008</t>
-  </si>
-  <si>
-    <t>0.9674,0.0107,0.0037,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0011,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0020,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9924,0.0075,0.0007,0.0002</t>
+    <t>0.0001,0.9995,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9992,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0119,0.9873,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.2717,0.0232,0.5406,0.0018</t>
+  </si>
+  <si>
+    <t>0.8510,0.0105,0.0953,0.0010</t>
+  </si>
+  <si>
+    <t>0.2422,0.6661,0.0029,0.0042</t>
+  </si>
+  <si>
+    <t>0.8860,0.0187,0.0280,0.0025</t>
+  </si>
+  <si>
+    <t>0.0004,0.9665,0.0026,0.0771</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9969,0.2890,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9995,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0170,0.9874,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0539,0.9559,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.9951,0.0040,0.0005,0.0001</t>
   </si>
   <si>
     <t>0.9993,0.0003,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9993,0.0002,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.1684,0.8448,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0443,0.9633,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0586,0.9598,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.8591,0.1225,0.0068,0.0006</t>
-  </si>
-  <si>
-    <t>0.1436,0.9094,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9951,0.0024,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9868,0.0155,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.6203,0.4970,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0086,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.4767,0.4035,0.0270,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.0017,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0115,0.4194,0.6475,0.0032</t>
-  </si>
-  <si>
-    <t>0.0010,0.0169,0.9962,0.0000</t>
-  </si>
-  <si>
-    <t>0.0243,0.0416,0.9192,0.0016</t>
-  </si>
-  <si>
-    <t>0.0001,0.2260,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0016,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0048,0.0232,0.9839,0.0004</t>
-  </si>
-  <si>
-    <t>0.1510,0.0110,0.7900,0.0012</t>
-  </si>
-  <si>
-    <t>0.0235,0.6707,0.3065,0.0004</t>
-  </si>
-  <si>
-    <t>0.0212,0.9554,0.0108,0.0002</t>
-  </si>
-  <si>
-    <t>0.0166,0.9657,0.0094,0.0004</t>
-  </si>
-  <si>
-    <t>0.5023,0.3806,0.0225,0.0011</t>
-  </si>
-  <si>
-    <t>0.9716,0.0023,0.0074,0.0003</t>
-  </si>
-  <si>
-    <t>0.1078,0.8151,0.0234,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.9991,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0052,0.9946,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.3960,0.7189,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0049,0.9950,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.5114,0.4569,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9857,0.0018,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.9756,0.0069,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.1483,0.0749,0.6456,0.0014</t>
-  </si>
-  <si>
-    <t>0.3159,0.0976,0.3060,0.0031</t>
-  </si>
-  <si>
-    <t>0.0005,0.0048,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0377,0.5302,0.1858,0.0017</t>
-  </si>
-  <si>
-    <t>0.0365,0.0952,0.7954,0.0026</t>
-  </si>
-  <si>
-    <t>0.0185,0.0344,0.9085,0.0020</t>
-  </si>
-  <si>
-    <t>0.2648,0.0232,0.4556,0.0097</t>
-  </si>
-  <si>
-    <t>0.9771,0.0240,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9869,0.0158,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9397,0.0649,0.0037,0.0006</t>
-  </si>
-  <si>
-    <t>0.8401,0.2426,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.9723,0.0374,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9078,0.0983,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.9912,0.0041,0.0021,0.0011</t>
-  </si>
-  <si>
-    <t>0.9953,0.0028,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0064,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.1774,0.6385,0.0750,0.0006</t>
-  </si>
-  <si>
-    <t>0.9736,0.0045,0.0066,0.0007</t>
-  </si>
-  <si>
-    <t>0.0005,0.0004,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.0253,0.9821,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.0015,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0173,0.0174,0.9535,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.0010,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.3910,0.9784,0.0001</t>
-  </si>
-  <si>
-    <t>0.0285,0.0085,0.9496,0.0014</t>
-  </si>
-  <si>
-    <t>0.8602,0.0133,0.0677,0.0010</t>
-  </si>
-  <si>
-    <t>0.9492,0.0013,0.0453,0.0003</t>
-  </si>
-  <si>
-    <t>0.9807,0.0083,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9744,0.0263,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.7237,0.4385,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9855,0.0226,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.8849,0.1868,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9850,0.0213,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9884,0.0137,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9892,0.0101,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.0239,0.7995,0.1581,0.0045</t>
-  </si>
-  <si>
-    <t>0.0030,0.1642,0.9640,0.0005</t>
-  </si>
-  <si>
-    <t>0.0067,0.0823,0.9507,0.0015</t>
-  </si>
-  <si>
-    <t>0.0055,0.4781,0.6961,0.0003</t>
-  </si>
-  <si>
-    <t>0.0012,0.0029,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.2008,0.0024,0.7833,0.0035</t>
-  </si>
-  <si>
-    <t>0.0206,0.0214,0.9512,0.0014</t>
-  </si>
-  <si>
-    <t>0.0425,0.0001,0.9420,0.0016</t>
-  </si>
-  <si>
-    <t>0.9949,0.0011,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.0065,0.0004,0.0002,0.9973</t>
-  </si>
-  <si>
-    <t>0.0176,0.0003,0.0010,0.9947</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0003,0.9999</t>
-  </si>
-  <si>
-    <t>0.0011,0.0000,0.0001,0.9996</t>
-  </si>
-  <si>
-    <t>0.9827,0.0018,0.0035,0.0007</t>
+    <t>0.9953,0.0022,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.9970,0.0010,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9977,0.0011,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9690,0.0265,0.0036,0.0002</t>
+  </si>
+  <si>
+    <t>0.9964,0.0026,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9957,0.0017,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.8399,0.8934,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.2541,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.7614,0.9456,0.0000</t>
+  </si>
+  <si>
+    <t>0.4607,0.0611,0.1842,0.0013</t>
+  </si>
+  <si>
+    <t>0.9925,0.0006,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.5855,0.0497,0.1820,0.0017</t>
+  </si>
+  <si>
+    <t>0.2563,0.0002,0.8602,0.0001</t>
+  </si>
+  <si>
+    <t>0.3805,0.4371,0.0263,0.0008</t>
+  </si>
+  <si>
+    <t>0.5542,0.0003,0.0040,0.5854</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0014,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.0456,0.9962</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.0855,0.0000</t>
+  </si>
+  <si>
+    <t>0.9956,0.0033,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9989,0.0003,0.0028</t>
+  </si>
+  <si>
+    <t>0.9962,0.0010,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.0014,0.9973,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0010,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.5873,0.0004,0.0015,0.4516</t>
+  </si>
+  <si>
+    <t>0.0058,0.0984,0.9594,0.0063</t>
+  </si>
+  <si>
+    <t>0.9743,0.0003,0.0163,0.0008</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.0038,0.9969,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9830,0.0055,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.8616,0.0545,0.0304,0.0006</t>
+  </si>
+  <si>
+    <t>0.0091,0.9872,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.8440,0.1494,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.9408,0.0326,0.0028,0.0005</t>
+  </si>
+  <si>
+    <t>0.9985,0.0009,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9968,0.0020,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0016,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9974,0.0021,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.1367,0.8103,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.0917,0.9443,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0095,0.9898,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0065,0.6376,0.8404,0.0002</t>
+  </si>
+  <si>
+    <t>0.6959,0.3914,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9940,0.0023,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9797,0.0267,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.8462,0.2435,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0448,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.6417,0.1272,0.0720,0.0005</t>
+  </si>
+  <si>
+    <t>0.0005,0.0111,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0228,0.0639,0.9164,0.0022</t>
+  </si>
+  <si>
+    <t>0.0010,0.0089,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0393,0.0805,0.8509,0.0034</t>
+  </si>
+  <si>
+    <t>0.0001,0.0089,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0118,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0131,0.0351,0.9596,0.0004</t>
+  </si>
+  <si>
+    <t>0.0300,0.0046,0.9619,0.0002</t>
+  </si>
+  <si>
+    <t>0.0512,0.0354,0.8913,0.0005</t>
+  </si>
+  <si>
+    <t>0.0502,0.6592,0.1415,0.0002</t>
+  </si>
+  <si>
+    <t>0.0033,0.8913,0.3566,0.0001</t>
+  </si>
+  <si>
+    <t>0.8280,0.0701,0.0351,0.0022</t>
+  </si>
+  <si>
+    <t>0.6017,0.2414,0.0205,0.0011</t>
+  </si>
+  <si>
+    <t>0.2147,0.4741,0.0779,0.0006</t>
+  </si>
+  <si>
+    <t>0.0005,0.9992,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9993,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0320,0.9763,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.1609,0.8827,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.0285,0.9776,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0094,0.9836,0.0019,0.0005</t>
+  </si>
+  <si>
+    <t>0.9878,0.0006,0.0038,0.0001</t>
+  </si>
+  <si>
+    <t>0.9436,0.0180,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.7153,0.0976,0.0928,0.0021</t>
+  </si>
+  <si>
+    <t>0.4334,0.0112,0.5592,0.0013</t>
+  </si>
+  <si>
+    <t>0.0007,0.0025,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.4258,0.2288,0.0106,0.0027</t>
+  </si>
+  <si>
+    <t>0.0085,0.0153,0.9699,0.0012</t>
+  </si>
+  <si>
+    <t>0.6143,0.0034,0.3236,0.0024</t>
+  </si>
+  <si>
+    <t>0.0215,0.0357,0.8844,0.0033</t>
+  </si>
+  <si>
+    <t>0.9974,0.0017,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9815,0.0211,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9001,0.0691,0.0086,0.0005</t>
+  </si>
+  <si>
+    <t>0.9565,0.0671,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9356,0.0862,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.8770,0.1732,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9429,0.0205,0.0121,0.0008</t>
+  </si>
+  <si>
+    <t>0.9977,0.0010,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0042,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0161,0.7685,0.2920,0.0003</t>
+  </si>
+  <si>
+    <t>0.7261,0.0063,0.1614,0.0039</t>
+  </si>
+  <si>
+    <t>0.0009,0.0008,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9365,0.7060,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0019,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.1228,0.0331,0.7935,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.0014,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.0023,0.1139,0.9704,0.0013</t>
+  </si>
+  <si>
+    <t>0.0132,0.2987,0.7314,0.0012</t>
+  </si>
+  <si>
+    <t>0.6916,0.1862,0.0148,0.0005</t>
+  </si>
+  <si>
+    <t>0.9749,0.0004,0.0198,0.0001</t>
+  </si>
+  <si>
+    <t>0.9586,0.0141,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.8963,0.1461,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.6973,0.4695,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9944,0.0084,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9487,0.0703,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9549,0.0763,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9932,0.0069,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9955,0.0033,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.1907,0.4505,0.1092,0.0025</t>
+  </si>
+  <si>
+    <t>0.0013,0.4339,0.9731,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.0114,0.9938,0.0004</t>
+  </si>
+  <si>
+    <t>0.0011,0.0317,0.9919,0.0002</t>
+  </si>
+  <si>
+    <t>0.0037,0.0004,0.9941,0.0006</t>
+  </si>
+  <si>
+    <t>0.3461,0.0015,0.6954,0.0006</t>
+  </si>
+  <si>
+    <t>0.0031,0.0063,0.9919,0.0002</t>
+  </si>
+  <si>
+    <t>0.0070,0.0020,0.9855,0.0008</t>
+  </si>
+  <si>
+    <t>0.9951,0.0006,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.0751,0.0038,0.0001,0.9642</t>
+  </si>
+  <si>
+    <t>0.1517,0.0004,0.0114,0.9105</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0008,0.9998</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.9700,0.0018,0.0133,0.0009</t>
   </si>
 </sst>
 </file>
@@ -1941,7 +1944,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1955,7 +1958,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1969,7 +1972,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1983,7 +1986,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1997,7 +2000,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2011,7 +2014,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2025,7 +2028,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2039,7 +2042,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2053,7 +2056,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2067,7 +2070,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2081,7 +2084,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2095,7 +2098,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2106,10 +2109,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2123,7 +2126,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2137,7 +2140,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2151,7 +2154,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2165,7 +2168,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2179,7 +2182,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2193,7 +2196,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2207,7 +2210,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2221,7 +2224,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2235,7 +2238,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2249,7 +2252,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2260,10 +2263,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2277,7 +2280,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2291,7 +2294,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2305,7 +2308,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2319,7 +2322,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2333,7 +2336,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2347,7 +2350,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2361,7 +2364,7 @@
         <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2375,7 +2378,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2389,7 +2392,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2403,7 +2406,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2417,7 +2420,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2431,7 +2434,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2445,7 +2448,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2459,7 +2462,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2473,7 +2476,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2484,10 +2487,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2501,7 +2504,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2515,7 +2518,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2529,7 +2532,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2543,7 +2546,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2557,7 +2560,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2571,7 +2574,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2585,7 +2588,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2599,7 +2602,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>284</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2613,7 +2616,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2627,7 +2630,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2641,7 +2644,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2655,7 +2658,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2669,7 +2672,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2683,7 +2686,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2697,7 +2700,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2711,7 +2714,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2725,7 +2728,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2739,7 +2742,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2753,7 +2756,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2767,7 +2770,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2781,7 +2784,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2795,7 +2798,7 @@
         <v>262</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2809,7 +2812,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2823,7 +2826,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2837,7 +2840,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2851,7 +2854,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2865,7 +2868,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2879,7 +2882,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2890,10 +2893,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2907,7 +2910,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2921,7 +2924,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2935,7 +2938,7 @@
         <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2949,7 +2952,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2963,7 +2966,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2977,7 +2980,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2991,7 +2994,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3005,7 +3008,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3019,7 +3022,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3033,7 +3036,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3047,7 +3050,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3061,7 +3064,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3075,7 +3078,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3089,7 +3092,7 @@
         <v>262</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3103,7 +3106,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3117,7 +3120,7 @@
         <v>262</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3131,7 +3134,7 @@
         <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3145,7 +3148,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3159,7 +3162,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3173,7 +3176,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3187,7 +3190,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3201,7 +3204,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3215,7 +3218,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3229,7 +3232,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3243,7 +3246,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3257,7 +3260,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3271,7 +3274,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3285,7 +3288,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3299,7 +3302,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3313,7 +3316,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3327,7 +3330,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3341,7 +3344,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3355,7 +3358,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3369,7 +3372,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3383,7 +3386,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3397,7 +3400,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3411,7 +3414,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3425,7 +3428,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3439,7 +3442,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3453,7 +3456,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>370</v>
+        <v>284</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3467,7 +3470,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3481,7 +3484,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3495,7 +3498,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>282</v>
+        <v>373</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3509,7 +3512,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>284</v>
+        <v>373</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3523,7 +3526,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3537,7 +3540,7 @@
         <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3551,7 +3554,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3562,10 +3565,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3579,7 +3582,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3590,10 +3593,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D120" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3607,7 +3610,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3621,7 +3624,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>379</v>
+        <v>313</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3635,7 +3638,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>380</v>
+        <v>285</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3649,7 +3652,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3663,7 +3666,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3677,7 +3680,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3691,7 +3694,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3705,7 +3708,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3719,7 +3722,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3733,7 +3736,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3747,7 +3750,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3761,7 +3764,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3775,7 +3778,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3789,7 +3792,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3803,7 +3806,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3817,7 +3820,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3831,7 +3834,7 @@
         <v>262</v>
       </c>
       <c r="D137" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3842,10 +3845,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3856,10 +3859,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D139" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3873,7 +3876,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3887,7 +3890,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3901,7 +3904,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3912,10 +3915,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D143" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3926,10 +3929,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D144" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3943,7 +3946,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3957,7 +3960,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3971,7 +3974,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3985,7 +3988,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3999,7 +4002,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4013,7 +4016,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4027,7 +4030,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4041,7 +4044,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4055,7 +4058,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4069,7 +4072,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4083,7 +4086,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>412</v>
+        <v>388</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4097,7 +4100,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4111,7 +4114,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4125,7 +4128,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4139,7 +4142,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4153,7 +4156,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4167,7 +4170,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4181,7 +4184,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4195,7 +4198,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4209,7 +4212,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4223,7 +4226,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4237,7 +4240,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4251,7 +4254,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4265,7 +4268,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4279,7 +4282,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4293,7 +4296,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4307,7 +4310,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4321,7 +4324,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4335,7 +4338,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4349,7 +4352,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4363,7 +4366,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4374,10 +4377,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4388,10 +4391,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4405,7 +4408,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4419,7 +4422,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4433,7 +4436,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4447,7 +4450,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4461,7 +4464,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4475,7 +4478,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4489,7 +4492,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4503,7 +4506,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4517,7 +4520,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4531,7 +4534,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4545,7 +4548,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4559,7 +4562,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4573,7 +4576,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4587,7 +4590,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4598,10 +4601,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4615,7 +4618,7 @@
         <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4629,7 +4632,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4643,7 +4646,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4657,7 +4660,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4668,10 +4671,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D197" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4685,7 +4688,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4699,7 +4702,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4713,7 +4716,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4727,7 +4730,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4741,7 +4744,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4752,10 +4755,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4769,7 +4772,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4783,7 +4786,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4794,10 +4797,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4808,10 +4811,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4825,7 +4828,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4836,10 +4839,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D209" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4853,7 +4856,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4864,10 +4867,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D211" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4878,10 +4881,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4895,7 +4898,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4909,7 +4912,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4923,7 +4926,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4937,7 +4940,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4951,7 +4954,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4965,7 +4968,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4979,7 +4982,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4993,7 +4996,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5007,7 +5010,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5021,7 +5024,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5035,7 +5038,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5049,7 +5052,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5063,7 +5066,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5074,10 +5077,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5091,7 +5094,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5105,7 +5108,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5119,7 +5122,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5133,7 +5136,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5147,7 +5150,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5161,7 +5164,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5175,7 +5178,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5189,7 +5192,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5203,7 +5206,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5217,7 +5220,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5231,7 +5234,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5245,7 +5248,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5259,7 +5262,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5273,7 +5276,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5287,7 +5290,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5301,7 +5304,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5312,10 +5315,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D243" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5329,7 +5332,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5343,7 +5346,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5357,7 +5360,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5371,7 +5374,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5385,7 +5388,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5399,7 +5402,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5413,7 +5416,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5427,7 +5430,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5441,7 +5444,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5455,7 +5458,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5469,7 +5472,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5483,7 +5486,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5497,7 +5500,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
